--- a/files/Supplementary_Tables/Supplementary_Table_S2.xlsx
+++ b/files/Supplementary_Tables/Supplementary_Table_S2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tina/Desktop/补充材料/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15EBC3F5-C16F-D341-94B6-7C7EBA0D52E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{119FF0B9-4B0C-254E-9976-206BFAE390CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{17AEE2DE-AFD0-7840-B7B3-213FC2FA3938}"/>
+    <workbookView xWindow="13520" yWindow="760" windowWidth="13180" windowHeight="16940" xr2:uid="{17AEE2DE-AFD0-7840-B7B3-213FC2FA3938}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -116,7 +116,7 @@
   </si>
   <si>
     <r>
-      <t>Note: Superpositions were performed in PyMOL 3.1.6.1 using the align command with chain C as the reference. The difference between “Initial aligned atoms” and “Refined atoms” (0-16 atoms per mutant) consists exclusively of side</t>
+      <t>Note: Superpositions were performed in PyMOL 3.1.6.1 using the 'align'  command with chain C as the reference. The difference between “Initial aligned atoms” and “Refined atoms” (0-16 atoms per mutant) consists exclusively of s</t>
     </r>
     <r>
       <rPr>
@@ -125,7 +125,7 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">‑chain atoms at the mutated positions, which were rejected during a single pruning cycle. All refined atom pairs yielded an RMSD of 0.000 Å, confirming that none of the alanine substitutions caused backbone conformational changes. </t>
+      <t xml:space="preserve">ide‑chain atoms at the mutated positions, which were rejected during a single pruning cycle. All refined atom pairs yielded an RMSD of 0.000 Å, confirming that none of the alanine substitutions caused backbone conformational changes. </t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
